--- a/AI_AuditLog_NguyenNgocBuu.xlsx
+++ b/AI_AuditLog_NguyenNgocBuu.xlsx
@@ -1,31 +1,48 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FPT\SUM2026\MMA303\Group4\mma301-su26-mma301_se19b05_group-04\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SU26\mmasp26\mma301-su26-mma301_se19b05_group-04\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DD65397C-F145-4BC5-9DF4-E40B68736556}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C384626-00C4-4A47-8982-D30916F91E74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-158" yWindow="0" windowWidth="16201" windowHeight="9307" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AI_AuditLog" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
+  <metadataTypes count="1">
+    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLRICHVALUE" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <valueMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </valueMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>Buổi</t>
   </si>
@@ -64,6 +81,21 @@
   </si>
   <si>
     <t>db-design.png</t>
+  </si>
+  <si>
+    <t>27/5/2026</t>
+  </si>
+  <si>
+    <t>Thết kế các chức năng Redux component,counter component</t>
+  </si>
+  <si>
+    <t>Gợi ý các chức năng liên quan tới redux,counter component</t>
+  </si>
+  <si>
+    <t>useReducer, kèm theo một mẫu cấu trúc CRUD (Thêm, Đọc, Sửa, Xóa)</t>
+  </si>
+  <si>
+    <t>Hiểu rõ hơn về Redux,Counter component</t>
   </si>
 </sst>
 </file>
@@ -109,7 +141,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Bình thường" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -122,6 +154,70 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
+<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
+  <global>
+    <keyFlags>
+      <key name="_Self">
+        <flag name="ExcludeFromFile" value="1"/>
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_DisplayString">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Flags">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Format">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_SubLabel">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Attribution">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Icon">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Display">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_CanonicalPropertyNames">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_ClassificationId">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+    </keyFlags>
+  </global>
+</rvTypesInfo>
+</file>
+
+<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <rv s="0">
+    <v>0</v>
+    <v>5</v>
+  </rv>
+</rvData>
+</file>
+
+<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <s t="_localImage">
+    <k n="_rvRel:LocalImageIdentifier" t="i"/>
+    <k n="CalcOrigin" t="i"/>
+  </s>
+</rvStructures>
+</file>
+
+<file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
+<richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <rel r:id="rId1"/>
+</richValueRels>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -409,8 +505,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:G3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
@@ -421,7 +517,7 @@
     <col min="7" max="7" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -444,7 +540,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -465,6 +561,29 @@
       </c>
       <c r="G2" t="s">
         <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" t="e" vm="1">
+        <v>#VALUE!</v>
       </c>
     </row>
   </sheetData>
